--- a/docs/example/delivery-note-export.xlsx
+++ b/docs/example/delivery-note-export.xlsx
@@ -67,15 +67,15 @@
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <family val="2"/>
       <b val="1"/>
       <color/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">

--- a/docs/example/delivery-note-export.xlsx
+++ b/docs/example/delivery-note-export.xlsx
@@ -43,7 +43,7 @@
     <t>DN-00001/GNS/X/2026</t>
   </si>
   <si>
-    <t>2026-10-10</t>
+    <t>2026-10-11</t>
   </si>
   <si>
     <t>PO/SCN/2026/0088</t>

--- a/docs/example/delivery-note-export.xlsx
+++ b/docs/example/delivery-note-export.xlsx
@@ -98,13 +98,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -402,28 +405,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>19560420</v>
       </c>
     </row>

--- a/docs/example/delivery-note-export.xlsx
+++ b/docs/example/delivery-note-export.xlsx
@@ -43,7 +43,7 @@
     <t>DN-00001/GNS/X/2026</t>
   </si>
   <si>
-    <t>2026-10-11</t>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>PO/SCN/2026/0088</t>
